--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/post FET_HRM-2031-0300/Panel-28/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/post FET_HRM-2031-0300/Panel-28/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Front_Summary.xlsx
@@ -419,22 +419,32 @@
     <row r="1">
       <c r="C1" t="inlineStr">
         <is>
-          <t>Distance 1</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Distance 2</t>
+          <t>Min Stepheight</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Angle</t>
+          <t>Mean Stepheight</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Area</t>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -446,20 +456,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fiducial 1</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>128.25154</v>
+        <v>17.88009</v>
       </c>
       <c r="D2" t="n">
-        <v>92.3567</v>
+        <v>17.45175</v>
       </c>
       <c r="E2" t="n">
-        <v>95.33802</v>
+        <v>17.58172</v>
       </c>
       <c r="F2" t="n">
-        <v>550.56998</v>
+        <v>45.18565</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.05302</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.93564</v>
       </c>
     </row>
     <row r="3">
@@ -469,16 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>129.80675</v>
+        <v>17.81561</v>
       </c>
       <c r="D3" t="n">
-        <v>91.25067</v>
+        <v>17.61175</v>
       </c>
       <c r="E3" t="n">
-        <v>97.22739</v>
+        <v>17.72819</v>
       </c>
       <c r="F3" t="n">
-        <v>555.97202</v>
+        <v>45.19242</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.05509</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.95287</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>129.59287</v>
+        <v>17.76764</v>
       </c>
       <c r="D4" t="n">
-        <v>90.89191</v>
+        <v>17.67554</v>
       </c>
       <c r="E4" t="n">
-        <v>97.20995000000001</v>
+        <v>17.69041</v>
       </c>
       <c r="F4" t="n">
-        <v>544.89924</v>
+        <v>44.89862</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.05355</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.91753</v>
       </c>
     </row>
     <row r="5">
@@ -507,16 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>128.98843</v>
+        <v>18.00793</v>
       </c>
       <c r="D5" t="n">
-        <v>92.08806</v>
+        <v>17.76974</v>
       </c>
       <c r="E5" t="n">
-        <v>95.6551</v>
+        <v>17.94732</v>
       </c>
       <c r="F5" t="n">
-        <v>537.99901</v>
+        <v>44.38509</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.05456</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.9497</v>
       </c>
     </row>
     <row r="6">
@@ -526,16 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>129.44314</v>
+        <v>18.40811</v>
       </c>
       <c r="D6" t="n">
-        <v>92.74541000000001</v>
+        <v>17.61268</v>
       </c>
       <c r="E6" t="n">
-        <v>96.70967</v>
+        <v>17.90127</v>
       </c>
       <c r="F6" t="n">
-        <v>556.7753300000001</v>
+        <v>45.48484</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.91936</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>129.92242</v>
+        <v>17.86014</v>
       </c>
       <c r="D7" t="n">
-        <v>93.42451</v>
+        <v>17.45781</v>
       </c>
       <c r="E7" t="n">
-        <v>98.34524</v>
+        <v>17.6794</v>
       </c>
       <c r="F7" t="n">
-        <v>542.37679</v>
+        <v>44.31755</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.0547</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.93565</v>
       </c>
     </row>
     <row r="8">
@@ -564,16 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>130.43184</v>
+        <v>18.18629</v>
       </c>
       <c r="D8" t="n">
-        <v>91.77816</v>
+        <v>17.53041</v>
       </c>
       <c r="E8" t="n">
-        <v>96.68256</v>
+        <v>17.55787</v>
       </c>
       <c r="F8" t="n">
-        <v>557.26423</v>
+        <v>44.21582</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.05395</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.96412</v>
       </c>
     </row>
     <row r="9">
@@ -583,16 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>126.32757</v>
+        <v>17.82091</v>
       </c>
       <c r="D9" t="n">
-        <v>91.08078999999999</v>
+        <v>17.57548</v>
       </c>
       <c r="E9" t="n">
-        <v>97.15705</v>
+        <v>17.74299</v>
       </c>
       <c r="F9" t="n">
-        <v>546.92251</v>
+        <v>45.19234</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.05282</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.91023</v>
       </c>
     </row>
     <row r="10">
@@ -602,27 +660,53 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>129.89221</v>
+        <v>18.05304</v>
       </c>
       <c r="D10" t="n">
-        <v>89.08123000000001</v>
+        <v>17.86408</v>
       </c>
       <c r="E10" t="n">
-        <v>98.45990999999999</v>
+        <v>17.86922</v>
       </c>
       <c r="F10" t="n">
-        <v>541.87411</v>
+        <v>44.60326</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.05394</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.94214</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Height</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Diameter</t>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -634,14 +718,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Micro Bump 3</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9.1919</v>
+        <v>17.88555</v>
       </c>
       <c r="D12" t="n">
-        <v>25.73521</v>
+        <v>17.33674</v>
+      </c>
+      <c r="E12" t="n">
+        <v>17.73098</v>
+      </c>
+      <c r="F12" t="n">
+        <v>44.47139</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.05289</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.93858</v>
       </c>
     </row>
     <row r="13">
@@ -651,10 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9.248609999999999</v>
+        <v>17.68324</v>
       </c>
       <c r="D13" t="n">
-        <v>25.96221</v>
+        <v>17.5066</v>
+      </c>
+      <c r="E13" t="n">
+        <v>17.51501</v>
+      </c>
+      <c r="F13" t="n">
+        <v>44.28919</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.05406</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.85459</v>
       </c>
     </row>
     <row r="14">
@@ -664,10 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9.17844</v>
+        <v>18.00951</v>
       </c>
       <c r="D14" t="n">
-        <v>25.76383</v>
+        <v>17.34932</v>
+      </c>
+      <c r="E14" t="n">
+        <v>17.53904</v>
+      </c>
+      <c r="F14" t="n">
+        <v>44.39553</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.05328</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.87826</v>
       </c>
     </row>
     <row r="15">
@@ -677,10 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9.202070000000001</v>
+        <v>17.80133</v>
       </c>
       <c r="D15" t="n">
-        <v>25.77946</v>
+        <v>17.27003</v>
+      </c>
+      <c r="E15" t="n">
+        <v>17.57704</v>
+      </c>
+      <c r="F15" t="n">
+        <v>45.27698</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.05337</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.94537</v>
       </c>
     </row>
     <row r="16">
@@ -690,10 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9.267910000000001</v>
+        <v>17.83735</v>
       </c>
       <c r="D16" t="n">
-        <v>25.55779</v>
+        <v>17.76522</v>
+      </c>
+      <c r="E16" t="n">
+        <v>17.77823</v>
+      </c>
+      <c r="F16" t="n">
+        <v>45.41605</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.05338</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.99326</v>
       </c>
     </row>
     <row r="17">
@@ -703,10 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9.160259999999999</v>
+        <v>18.03306</v>
       </c>
       <c r="D17" t="n">
-        <v>25.78769</v>
+        <v>17.544</v>
+      </c>
+      <c r="E17" t="n">
+        <v>17.6433</v>
+      </c>
+      <c r="F17" t="n">
+        <v>44.76364</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.05325</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.90559</v>
       </c>
     </row>
     <row r="18">
@@ -716,10 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9.18191</v>
+        <v>17.78253</v>
       </c>
       <c r="D18" t="n">
-        <v>25.95097</v>
+        <v>17.60759</v>
+      </c>
+      <c r="E18" t="n">
+        <v>17.75401</v>
+      </c>
+      <c r="F18" t="n">
+        <v>45.77662</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.05304</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.92124</v>
       </c>
     </row>
     <row r="19">
@@ -729,10 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9.285030000000001</v>
+        <v>17.75276</v>
       </c>
       <c r="D19" t="n">
-        <v>25.89254</v>
+        <v>17.43966</v>
+      </c>
+      <c r="E19" t="n">
+        <v>17.56253</v>
+      </c>
+      <c r="F19" t="n">
+        <v>45.78672</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05405</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.91313</v>
       </c>
     </row>
     <row r="20">
@@ -742,39 +922,31 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9.134</v>
+        <v>18.03959</v>
       </c>
       <c r="D20" t="n">
-        <v>25.799</v>
+        <v>17.29965</v>
+      </c>
+      <c r="E20" t="n">
+        <v>17.6864</v>
+      </c>
+      <c r="F20" t="n">
+        <v>46.10563</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05358</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.91896</v>
       </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>Max Stepheight</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -788,26 +960,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>via 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>17.1294</v>
+        <v>0.6453100000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>17.82606</v>
-      </c>
-      <c r="E22" t="n">
-        <v>17.43843</v>
-      </c>
-      <c r="F22" t="n">
-        <v>45.24262</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.05255</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1.92848</v>
+        <v>1.21041</v>
       </c>
     </row>
     <row r="23">
@@ -817,22 +977,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>17.80696</v>
+        <v>0.64119</v>
       </c>
       <c r="D23" t="n">
-        <v>17.18332</v>
-      </c>
-      <c r="E23" t="n">
-        <v>17.78779</v>
-      </c>
-      <c r="F23" t="n">
-        <v>45.72987</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.05475</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1.9293</v>
+        <v>1.21905</v>
       </c>
     </row>
     <row r="24">
@@ -842,22 +990,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>17.71259</v>
+        <v>0.6457000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>17.52946</v>
-      </c>
-      <c r="E24" t="n">
-        <v>17.39186</v>
-      </c>
-      <c r="F24" t="n">
-        <v>45.48642</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.05401</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1.9285</v>
+        <v>1.19806</v>
       </c>
     </row>
     <row r="25">
@@ -867,22 +1003,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>17.57352</v>
+        <v>0.63226</v>
       </c>
       <c r="D25" t="n">
-        <v>17.39329</v>
-      </c>
-      <c r="E25" t="n">
-        <v>17.61879</v>
-      </c>
-      <c r="F25" t="n">
-        <v>44.38527</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1.87428</v>
+        <v>1.19432</v>
       </c>
     </row>
     <row r="26">
@@ -892,22 +1016,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>18.10057</v>
+        <v>0.64185</v>
       </c>
       <c r="D26" t="n">
-        <v>17.63387</v>
-      </c>
-      <c r="E26" t="n">
-        <v>17.56533</v>
-      </c>
-      <c r="F26" t="n">
-        <v>45.13405</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.05277</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1.91062</v>
+        <v>1.19202</v>
       </c>
     </row>
     <row r="27">
@@ -917,22 +1029,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>17.71216</v>
+        <v>0.64032</v>
       </c>
       <c r="D27" t="n">
-        <v>17.75458</v>
-      </c>
-      <c r="E27" t="n">
-        <v>17.77467</v>
-      </c>
-      <c r="F27" t="n">
-        <v>44.58731</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.05334</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1.92995</v>
+        <v>1.18511</v>
       </c>
     </row>
     <row r="28">
@@ -942,22 +1042,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>17.71352</v>
+        <v>0.63347</v>
       </c>
       <c r="D28" t="n">
-        <v>17.61301</v>
-      </c>
-      <c r="E28" t="n">
-        <v>17.93152</v>
-      </c>
-      <c r="F28" t="n">
-        <v>45.0288</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.05371</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1.91442</v>
+        <v>1.14595</v>
       </c>
     </row>
     <row r="29">
@@ -967,22 +1055,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>18.00938</v>
+        <v>0.63506</v>
       </c>
       <c r="D29" t="n">
-        <v>17.60325</v>
-      </c>
-      <c r="E29" t="n">
-        <v>17.94604</v>
-      </c>
-      <c r="F29" t="n">
-        <v>45.63108</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.05323</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1.92778</v>
+        <v>1.17838</v>
       </c>
     </row>
     <row r="30">
@@ -992,22 +1068,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>17.9078</v>
+        <v>0.64068</v>
       </c>
       <c r="D30" t="n">
-        <v>17.45761</v>
-      </c>
-      <c r="E30" t="n">
-        <v>17.45118</v>
-      </c>
-      <c r="F30" t="n">
-        <v>44.28413</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.05161</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1.94029</v>
+        <v>1.1742</v>
       </c>
     </row>
     <row r="31">
@@ -1064,28 +1128,28 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.80043</v>
+        <v>0.79518</v>
       </c>
       <c r="D32" t="n">
-        <v>0.08587</v>
+        <v>0.08597</v>
       </c>
       <c r="E32" t="n">
-        <v>0.63864</v>
+        <v>0.63678</v>
       </c>
       <c r="F32" t="n">
-        <v>1.03721</v>
+        <v>1.04712</v>
       </c>
       <c r="G32" t="n">
-        <v>0.11518</v>
+        <v>0.11374</v>
       </c>
       <c r="H32" t="n">
-        <v>0.008149999999999999</v>
+        <v>0.00817</v>
       </c>
       <c r="I32" t="n">
-        <v>0.09646</v>
+        <v>0.10117</v>
       </c>
       <c r="J32" t="n">
-        <v>0.13761</v>
+        <v>0.13335</v>
       </c>
     </row>
     <row r="33">
@@ -1095,28 +1159,28 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.78864</v>
+        <v>0.79526</v>
       </c>
       <c r="D33" t="n">
-        <v>0.08649</v>
+        <v>0.08585</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6526</v>
+        <v>0.63914</v>
       </c>
       <c r="F33" t="n">
-        <v>1.01766</v>
+        <v>1.01624</v>
       </c>
       <c r="G33" t="n">
-        <v>0.11479</v>
+        <v>0.11631</v>
       </c>
       <c r="H33" t="n">
-        <v>0.00808</v>
+        <v>0.00813</v>
       </c>
       <c r="I33" t="n">
-        <v>0.09893</v>
+        <v>0.09813</v>
       </c>
       <c r="J33" t="n">
-        <v>0.1359</v>
+        <v>0.13341</v>
       </c>
     </row>
     <row r="34">
@@ -1126,28 +1190,28 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.80411</v>
+        <v>0.77585</v>
       </c>
       <c r="D34" t="n">
-        <v>0.08565</v>
+        <v>0.08613999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>0.64093</v>
+        <v>0.63348</v>
       </c>
       <c r="F34" t="n">
-        <v>1.00734</v>
+        <v>1.03196</v>
       </c>
       <c r="G34" t="n">
-        <v>0.11836</v>
+        <v>0.11572</v>
       </c>
       <c r="H34" t="n">
-        <v>0.00788</v>
+        <v>0.00812</v>
       </c>
       <c r="I34" t="n">
-        <v>0.09923</v>
+        <v>0.10033</v>
       </c>
       <c r="J34" t="n">
-        <v>0.13493</v>
+        <v>0.13362</v>
       </c>
     </row>
     <row r="35">
@@ -1157,28 +1221,28 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.7884</v>
+        <v>0.81028</v>
       </c>
       <c r="D35" t="n">
-        <v>0.08629000000000001</v>
+        <v>0.08674</v>
       </c>
       <c r="E35" t="n">
-        <v>0.64062</v>
+        <v>0.64693</v>
       </c>
       <c r="F35" t="n">
-        <v>1.02176</v>
+        <v>1.00813</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1155</v>
+        <v>0.11659</v>
       </c>
       <c r="H35" t="n">
-        <v>0.007990000000000001</v>
+        <v>0.00796</v>
       </c>
       <c r="I35" t="n">
-        <v>0.09995</v>
+        <v>0.09809</v>
       </c>
       <c r="J35" t="n">
-        <v>0.13138</v>
+        <v>0.13504</v>
       </c>
     </row>
     <row r="36">
@@ -1188,25 +1252,25 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.8016799999999999</v>
+        <v>0.7952900000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0857</v>
+        <v>0.08537</v>
       </c>
       <c r="E36" t="n">
-        <v>0.65439</v>
+        <v>0.6299</v>
       </c>
       <c r="F36" t="n">
-        <v>1.02936</v>
+        <v>1.03763</v>
       </c>
       <c r="G36" t="n">
-        <v>0.11506</v>
+        <v>0.11856</v>
       </c>
       <c r="H36" t="n">
-        <v>0.00812</v>
+        <v>0.00821</v>
       </c>
       <c r="I36" t="n">
-        <v>0.09862</v>
+        <v>0.09898999999999999</v>
       </c>
       <c r="J36" t="n">
         <v>0.1333</v>
@@ -1219,28 +1283,28 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.79811</v>
+        <v>0.79826</v>
       </c>
       <c r="D37" t="n">
-        <v>0.08538999999999999</v>
+        <v>0.08562</v>
       </c>
       <c r="E37" t="n">
-        <v>0.65113</v>
+        <v>0.6442099999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>1.01853</v>
+        <v>1.0166</v>
       </c>
       <c r="G37" t="n">
-        <v>0.11531</v>
+        <v>0.11621</v>
       </c>
       <c r="H37" t="n">
-        <v>0.008070000000000001</v>
+        <v>0.008030000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0978</v>
+        <v>0.0993</v>
       </c>
       <c r="J37" t="n">
-        <v>0.13391</v>
+        <v>0.13301</v>
       </c>
     </row>
     <row r="38">
@@ -1250,28 +1314,28 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.7803600000000001</v>
+        <v>0.78476</v>
       </c>
       <c r="D38" t="n">
-        <v>0.08735999999999999</v>
+        <v>0.08694</v>
       </c>
       <c r="E38" t="n">
-        <v>0.64489</v>
+        <v>0.64294</v>
       </c>
       <c r="F38" t="n">
-        <v>1.00003</v>
+        <v>1.03335</v>
       </c>
       <c r="G38" t="n">
-        <v>0.11253</v>
+        <v>0.11572</v>
       </c>
       <c r="H38" t="n">
-        <v>0.007860000000000001</v>
+        <v>0.00795</v>
       </c>
       <c r="I38" t="n">
-        <v>0.09861</v>
+        <v>0.09833</v>
       </c>
       <c r="J38" t="n">
-        <v>0.1344</v>
+        <v>0.13582</v>
       </c>
     </row>
     <row r="39">
@@ -1281,28 +1345,28 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.78703</v>
+        <v>0.78389</v>
       </c>
       <c r="D39" t="n">
-        <v>0.08622</v>
+        <v>0.08636000000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>0.65787</v>
+        <v>0.64903</v>
       </c>
       <c r="F39" t="n">
-        <v>1.00097</v>
+        <v>1.01986</v>
       </c>
       <c r="G39" t="n">
-        <v>0.11459</v>
+        <v>0.11667</v>
       </c>
       <c r="H39" t="n">
-        <v>0.00801</v>
+        <v>0.00818</v>
       </c>
       <c r="I39" t="n">
-        <v>0.09909</v>
+        <v>0.09934999999999999</v>
       </c>
       <c r="J39" t="n">
-        <v>0.13585</v>
+        <v>0.13366</v>
       </c>
     </row>
     <row r="40">
@@ -1312,28 +1376,28 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.7921899999999999</v>
+        <v>0.79928</v>
       </c>
       <c r="D40" t="n">
-        <v>0.08756</v>
+        <v>0.08547</v>
       </c>
       <c r="E40" t="n">
-        <v>0.65384</v>
+        <v>0.64494</v>
       </c>
       <c r="F40" t="n">
-        <v>1.00393</v>
+        <v>1.02922</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1152</v>
+        <v>0.11479</v>
       </c>
       <c r="H40" t="n">
-        <v>0.007990000000000001</v>
+        <v>0.00791</v>
       </c>
       <c r="I40" t="n">
-        <v>0.09617000000000001</v>
+        <v>0.09923999999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>0.13527</v>
+        <v>0.13639</v>
       </c>
     </row>
   </sheetData>
